--- a/AAII_Financials/Quarterly/VFRM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VFRM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>VFRM</t>
   </si>
@@ -802,7 +802,7 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>300</v>
@@ -980,7 +980,7 @@
         <v>-1300</v>
       </c>
       <c r="H10" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
@@ -1475,8 +1475,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>1100</v>
       </c>
       <c r="E17" s="3">
         <v>1400</v>
@@ -1488,7 +1488,7 @@
         <v>2200</v>
       </c>
       <c r="H17" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="I17" s="3">
         <v>800</v>
@@ -1564,8 +1564,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
         <v>-1200</v>
@@ -1686,8 +1686,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1775,8 +1775,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-700</v>
       </c>
       <c r="E21" s="3">
         <v>-1200</v>
@@ -2220,8 +2220,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-1100</v>
       </c>
       <c r="E26" s="3">
         <v>-1400</v>
@@ -2309,8 +2309,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-1200</v>
       </c>
       <c r="E27" s="3">
         <v>-1500</v>
@@ -2754,8 +2754,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -2843,8 +2843,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-1200</v>
       </c>
       <c r="E33" s="3">
         <v>-1500</v>
@@ -3021,8 +3021,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-1200</v>
       </c>
       <c r="E35" s="3">
         <v>-1500</v>
@@ -3983,7 +3983,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>2600</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -6489,8 +6489,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-1200</v>
       </c>
       <c r="E81" s="3">
         <v>-1500</v>
